--- a/HolidayCalendarService/Template/Dynamics 365 Sales Deutsch.xlsx
+++ b/HolidayCalendarService/Template/Dynamics 365 Sales Deutsch.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://microsoft-my.sharepoint-df.com/personal/nicoschreder_microsoft_com/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicoschreder\Development\adventcalendarapp\HolidayCalendarService\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="74" documentId="8_{110DDB8F-EBA1-4859-B649-66EC3D68F6D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65C4F17C-3F48-4646-825A-E959667A177C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EF81703-AB46-42C7-9D68-468DC6D0999F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{DA429942-75DC-4399-AA24-F29984099B9A}"/>
   </bookViews>
@@ -189,22 +189,22 @@
     <t>Update deine Sales Stage.</t>
   </si>
   <si>
-    <t>https://github.com/nschreder/holidaycalendarapp/tree/main/HolidayCalendarService/Dynamics%20365%20Sales/6.jpg</t>
-  </si>
-  <si>
-    <t>https://github.com/nschreder/holidaycalendarapp/tree/main/HolidayCalendarService/Dynamics%20365%20Sales/15.jpg</t>
-  </si>
-  <si>
-    <t>https://github.com/nschreder/holidaycalendarapp/tree/main/HolidayCalendarService/Dynamics%20365%20Sales/19.jpg</t>
-  </si>
-  <si>
-    <t>https://github.com/nschreder/holidaycalendarapp/tree/main/HolidayCalendarService/Dynamics%20365%20Sales/22.jpg</t>
-  </si>
-  <si>
-    <t>https://github.com/nschreder/holidaycalendarapp/tree/main/HolidayCalendarService/Dynamics%20365%20Sales/24.jpg</t>
-  </si>
-  <si>
-    <t>https://github.com/nschreder/holidaycalendarapp/tree/main/HolidayCalendarService/Dynamics%20365%20Sales/11.jpg</t>
+    <t>https://raw.githubusercontent.com/nschreder/holidaycalendarapp/main/HolidayCalendarService/Dynamics%20365%20Sales/6.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/nschreder/holidaycalendarapp/main/HolidayCalendarService/Dynamics%20365%20Sales/10.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/nschreder/holidaycalendarapp/main/HolidayCalendarService/Dynamics%20365%20Sales/15.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/nschreder/holidaycalendarapp/main/HolidayCalendarService/Dynamics%20365%20Sales/19.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/nschreder/holidaycalendarapp/main/HolidayCalendarService/Dynamics%20365%20Sales/22.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/nschreder/holidaycalendarapp/main/HolidayCalendarService/Dynamics%20365%20Sales/24.jpg</t>
   </si>
 </sst>
 </file>
@@ -755,7 +755,7 @@
         <v>44905</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D11" t="s">
         <v>9</v>
@@ -825,7 +825,7 @@
         <v>44910</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
         <v>9</v>
@@ -881,7 +881,7 @@
         <v>44914</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D20" t="s">
         <v>9</v>
@@ -923,7 +923,7 @@
         <v>44917</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D23" t="s">
         <v>9</v>
@@ -951,7 +951,7 @@
         <v>44919</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D25" t="s">
         <v>9</v>
@@ -959,10 +959,18 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="C7" r:id="rId1" xr:uid="{499EC808-D27E-412E-A1D6-ED640E9E2D11}"/>
+    <hyperlink ref="C11" r:id="rId2" xr:uid="{55D89F68-8741-450D-BB2A-EF08CCD7EA65}"/>
+    <hyperlink ref="C16" r:id="rId3" xr:uid="{45965A93-C1EA-4B4B-9508-5F2B14B9CDDB}"/>
+    <hyperlink ref="C20" r:id="rId4" xr:uid="{DD335267-3C08-43ED-B80A-288BFBC808A4}"/>
+    <hyperlink ref="C23" r:id="rId5" xr:uid="{DDD06500-AEFA-4E90-9CD9-9A2C8542D780}"/>
+    <hyperlink ref="C25" r:id="rId6" xr:uid="{2AD4C968-792A-4C90-B10C-72533B6E15A2}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId7"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId8"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">

--- a/HolidayCalendarService/Template/Dynamics 365 Sales Deutsch.xlsx
+++ b/HolidayCalendarService/Template/Dynamics 365 Sales Deutsch.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicoschreder\Development\adventcalendarapp\HolidayCalendarService\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EF81703-AB46-42C7-9D68-468DC6D0999F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20B198B6-888F-4726-81D6-321CC27747D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{DA429942-75DC-4399-AA24-F29984099B9A}"/>
   </bookViews>
@@ -165,9 +165,6 @@
     <t>Navigiere durch D365 innerhalb von Outlook.</t>
   </si>
   <si>
-    <t>Basic navigation in App for Outlook (Dynamics 365 apps) | Microsoft Learn</t>
-  </si>
-  <si>
     <t>https://learn.microsoft.com/en-us/training/dynamics365/</t>
   </si>
   <si>
@@ -177,9 +174,6 @@
     <t>Erstelle deinen eigenen Flow.</t>
   </si>
   <si>
-    <t>Create a cloud flow with Dynamics 365 (online) - Power Automate | Microsoft Learn</t>
-  </si>
-  <si>
     <t>Binde deinen Teams Chat in Dynamics 365 ein.</t>
   </si>
   <si>
@@ -205,6 +199,12 @@
   </si>
   <si>
     <t>https://raw.githubusercontent.com/nschreder/holidaycalendarapp/main/HolidayCalendarService/Dynamics%20365%20Sales/24.jpg</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/power-automate/connection-dynamics365</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/de-de/dynamics365/outlook-app/user/basic-navigation</t>
   </si>
 </sst>
 </file>
@@ -255,11 +255,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -699,7 +700,7 @@
         <v>44901</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D7" t="s">
         <v>9</v>
@@ -755,7 +756,7 @@
         <v>44905</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s">
         <v>9</v>
@@ -825,7 +826,7 @@
         <v>44910</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s">
         <v>9</v>
@@ -852,8 +853,8 @@
       <c r="B18" s="1">
         <v>44912</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>42</v>
+      <c r="C18" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="D18" t="s">
         <v>4</v>
@@ -867,7 +868,7 @@
         <v>44913</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D19" t="s">
         <v>4</v>
@@ -875,13 +876,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B20" s="1">
         <v>44914</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D20" t="s">
         <v>9</v>
@@ -889,13 +890,13 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B21" s="1">
         <v>44915</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>46</v>
+      <c r="C21" s="4" t="s">
+        <v>54</v>
       </c>
       <c r="D21" t="s">
         <v>4</v>
@@ -903,13 +904,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B22" s="1">
         <v>44916</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D22" t="s">
         <v>4</v>
@@ -917,13 +918,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B23" s="1">
         <v>44917</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D23" t="s">
         <v>9</v>
@@ -951,7 +952,7 @@
         <v>44919</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D25" t="s">
         <v>9</v>
@@ -966,11 +967,13 @@
     <hyperlink ref="C20" r:id="rId4" xr:uid="{DD335267-3C08-43ED-B80A-288BFBC808A4}"/>
     <hyperlink ref="C23" r:id="rId5" xr:uid="{DDD06500-AEFA-4E90-9CD9-9A2C8542D780}"/>
     <hyperlink ref="C25" r:id="rId6" xr:uid="{2AD4C968-792A-4C90-B10C-72533B6E15A2}"/>
+    <hyperlink ref="C21" r:id="rId7" xr:uid="{121F1EDB-1E68-49D3-8DB4-A5F12D7F9B7A}"/>
+    <hyperlink ref="C18" r:id="rId8" xr:uid="{DA4A6B1C-7CAE-4F05-BDFC-9BD63EA8C6CF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId7"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId9"/>
   <tableParts count="1">
-    <tablePart r:id="rId8"/>
+    <tablePart r:id="rId10"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
